--- a/output/pdf_financials_xlsx/FLM.xlsx
+++ b/output/pdf_financials_xlsx/FLM.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.15979</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.116473</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.04115</v>
       </c>
     </row>
     <row r="13">
@@ -879,13 +879,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.248977</v>
+        <v>-2.408767</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.363007</v>
+        <v>-1.47948</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.428692</v>
+        <v>-1.469842</v>
       </c>
     </row>
     <row r="28">
@@ -911,13 +911,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.248977</v>
+        <v>-2.408767</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.363007</v>
+        <v>-1.47948</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.428692</v>
+        <v>-1.469842</v>
       </c>
     </row>
     <row r="30">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4998,7 +4998,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E63" s="5" t="n">

--- a/output/pdf_financials_xlsx/FLM.xlsx
+++ b/output/pdf_financials_xlsx/FLM.xlsx
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="8">
@@ -4725,7 +4725,11 @@
           <t>Directors’ fees (Note 8)</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E54" s="5" t="n">
         <v>0.03</v>
       </c>
